--- a/diseases/d210/2026-2029.xlsx
+++ b/diseases/d210/2026-2029.xlsx
@@ -1166,7 +1166,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7363,7 +7363,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -8168,7 +8168,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8575,7 +8575,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8817,7 +8817,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9229,7 +9229,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9883,7 +9883,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10125,7 +10125,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10779,7 +10779,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11342,7 +11342,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11749,7 +11749,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11991,7 +11991,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12403,7 +12403,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12645,7 +12645,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -13057,7 +13057,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -13299,7 +13299,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13711,7 +13711,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13953,7 +13953,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -14516,7 +14516,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14923,7 +14923,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15165,7 +15165,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -15577,7 +15577,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -15819,7 +15819,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -16231,7 +16231,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16473,7 +16473,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -16885,7 +16885,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -17127,7 +17127,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -17539,7 +17539,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17781,7 +17781,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -18182,7 +18182,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18578,7 +18578,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -18985,7 +18985,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -19227,7 +19227,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -19639,7 +19639,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19881,7 +19881,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -20293,7 +20293,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -20535,7 +20535,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -20947,7 +20947,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -21189,7 +21189,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -21590,7 +21590,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -21986,7 +21986,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -22393,7 +22393,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -22635,7 +22635,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -23047,7 +23047,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -23289,7 +23289,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -23701,7 +23701,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -23943,7 +23943,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -24355,7 +24355,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -24597,7 +24597,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -24754,16 +24754,16 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O115" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q115" t="n">
         <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>0.01836405909759895</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -24916,10 +24916,10 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O116" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U116" t="inlineStr">
         <is>
@@ -24998,7 +24998,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -25150,16 +25150,16 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O117" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>0.02607415467862137</v>
+        <v>0.03041984712505827</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -25312,10 +25312,10 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O118" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U118" t="inlineStr">
         <is>
@@ -25394,7 +25394,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -25801,7 +25801,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -26043,7 +26043,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -26311,7 +26311,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1930</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d210/2026-2029.xlsx
+++ b/diseases/d210/2026-2029.xlsx
@@ -1166,7 +1166,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7363,7 +7363,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -8168,7 +8168,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8575,7 +8575,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8817,7 +8817,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9229,7 +9229,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9883,7 +9883,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10125,7 +10125,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10779,7 +10779,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11342,7 +11342,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11749,7 +11749,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11991,7 +11991,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12403,7 +12403,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12645,7 +12645,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -13057,7 +13057,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -13299,7 +13299,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13711,7 +13711,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13953,7 +13953,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -14516,7 +14516,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14923,7 +14923,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15165,7 +15165,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -15577,7 +15577,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -15819,7 +15819,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -16231,7 +16231,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16473,7 +16473,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -16885,7 +16885,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -17127,7 +17127,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -17539,7 +17539,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17781,7 +17781,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -18182,7 +18182,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18578,7 +18578,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -18985,7 +18985,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -19227,7 +19227,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -19639,7 +19639,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19881,7 +19881,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -20293,7 +20293,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -20535,7 +20535,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -20947,7 +20947,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -21189,7 +21189,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -21346,16 +21346,16 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O99" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>0.2203687091711874</v>
+        <v>0.2240415209907072</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -21508,10 +21508,10 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O100" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="U100" t="inlineStr">
         <is>
@@ -21590,7 +21590,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -21986,7 +21986,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -22393,7 +22393,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -22635,7 +22635,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -23047,7 +23047,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -23289,7 +23289,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -23701,7 +23701,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -23943,7 +23943,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -24355,7 +24355,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -24597,7 +24597,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -24754,16 +24754,16 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O115" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q115" t="n">
         <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>0.01836405909759895</v>
+        <v>0.02570968273663853</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -24916,10 +24916,10 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O116" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U116" t="inlineStr">
         <is>
@@ -24998,7 +24998,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -25150,16 +25150,16 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O117" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>0.03041984712505827</v>
+        <v>0.03911123201793206</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -25312,10 +25312,10 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O118" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U118" t="inlineStr">
         <is>
@@ -25394,7 +25394,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -25801,7 +25801,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -26043,7 +26043,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -26311,7 +26311,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1936</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d210/2026-2029.xlsx
+++ b/diseases/d210/2026-2029.xlsx
@@ -21742,16 +21742,16 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O101" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q101" t="n">
         <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>0.1999018525360972</v>
+        <v>0.2042475449825341</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -21904,10 +21904,10 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O102" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U102" t="inlineStr">
         <is>
@@ -25150,16 +25150,16 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="O117" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>0.03911123201793206</v>
+        <v>0.06083969425011655</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -25312,10 +25312,10 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="O118" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="U118" t="inlineStr">
         <is>
@@ -26311,7 +26311,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1941</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d210/2026-2029.xlsx
+++ b/diseases/d210/2026-2029.xlsx
@@ -1176,7 +1176,7 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN4" t="b">
@@ -1326,9 +1326,6 @@
       <c r="P5" t="n">
         <v>2</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -1980,9 +1977,6 @@
       <c r="P8" t="n">
         <v>39</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.0111736487178006</v>
       </c>
@@ -2634,9 +2628,6 @@
       <c r="P11" t="n">
         <v>37</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0.01060064109124673</v>
       </c>
@@ -3288,9 +3279,6 @@
       <c r="P14" t="n">
         <v>43</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.01231966397090836</v>
       </c>
@@ -3942,9 +3930,6 @@
       <c r="P17" t="n">
         <v>27</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0.007735602958477341</v>
       </c>
@@ -5004,7 +4989,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN22" t="b">
@@ -5154,9 +5139,6 @@
       <c r="P23" t="n">
         <v>61</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0.01747673260989325</v>
       </c>
@@ -5808,9 +5790,6 @@
       <c r="P26" t="n">
         <v>37</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.01060064109124673</v>
       </c>
@@ -6462,9 +6441,6 @@
       <c r="P29" t="n">
         <v>31</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.008881618211585096</v>
       </c>
@@ -7116,9 +7092,6 @@
       <c r="P32" t="n">
         <v>36</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.01031413727796979</v>
       </c>
@@ -8178,7 +8151,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8328,9 +8301,6 @@
       <c r="P38" t="n">
         <v>34</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.00974112965141591</v>
       </c>
@@ -8982,9 +8952,6 @@
       <c r="P41" t="n">
         <v>45</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.01289267159746223</v>
       </c>
@@ -9636,9 +9603,6 @@
       <c r="P44" t="n">
         <v>39</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.0111736487178006</v>
       </c>
@@ -10290,9 +10254,6 @@
       <c r="P47" t="n">
         <v>43</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0.01231966397090836</v>
       </c>
@@ -10941,9 +10902,6 @@
       <c r="O50" t="n">
         <v>75</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.2754608864639843</v>
       </c>
@@ -11103,9 +11061,6 @@
       <c r="O51" t="n">
         <v>47</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0.2042475449825341</v>
       </c>
@@ -11352,7 +11307,7 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN52" t="b">
@@ -11502,9 +11457,6 @@
       <c r="P53" t="n">
         <v>53</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.01518470210367774</v>
       </c>
@@ -12156,9 +12108,6 @@
       <c r="P56" t="n">
         <v>39</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.0111736487178006</v>
       </c>
@@ -12810,9 +12759,6 @@
       <c r="P59" t="n">
         <v>37</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0.01060064109124673</v>
       </c>
@@ -13464,9 +13410,6 @@
       <c r="P62" t="n">
         <v>34</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.00974112965141591</v>
       </c>
@@ -14115,9 +14058,6 @@
       <c r="O65" t="n">
         <v>108</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.3966636765081373</v>
       </c>
@@ -14277,9 +14217,6 @@
       <c r="O66" t="n">
         <v>27</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.1173336960537962</v>
       </c>
@@ -14526,7 +14463,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14676,9 +14613,6 @@
       <c r="P68" t="n">
         <v>40</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.01146015253107754</v>
       </c>
@@ -15330,9 +15264,6 @@
       <c r="P71" t="n">
         <v>40</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0.01146015253107754</v>
       </c>
@@ -15984,9 +15915,6 @@
       <c r="P74" t="n">
         <v>33</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.009454625838138971</v>
       </c>
@@ -16638,9 +16566,6 @@
       <c r="P77" t="n">
         <v>16</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0.004584061012431017</v>
       </c>
@@ -17292,9 +17217,6 @@
       <c r="P80" t="n">
         <v>14</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.00401105338587714</v>
       </c>
@@ -17943,9 +17865,6 @@
       <c r="O83" t="n">
         <v>111</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0.4076821119666967</v>
       </c>
@@ -18339,9 +18258,6 @@
       <c r="O85" t="n">
         <v>35</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0.1520992356252913</v>
       </c>
@@ -18588,7 +18504,7 @@
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN86" t="b">
@@ -18738,9 +18654,6 @@
       <c r="P87" t="n">
         <v>32</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0.009168122024862033</v>
       </c>
@@ -19392,9 +19305,6 @@
       <c r="P90" t="n">
         <v>21</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.006016580078815709</v>
       </c>
@@ -20046,9 +19956,6 @@
       <c r="P93" t="n">
         <v>36</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0.01031413727796979</v>
       </c>
@@ -20700,9 +20607,6 @@
       <c r="P96" t="n">
         <v>35</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.01002763346469285</v>
       </c>
@@ -21351,9 +21255,6 @@
       <c r="O99" t="n">
         <v>61</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.2240415209907072</v>
       </c>
@@ -21747,9 +21648,6 @@
       <c r="O101" t="n">
         <v>47</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0.2042475449825341</v>
       </c>
@@ -21996,7 +21894,7 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN102" t="b">
@@ -22146,9 +22044,6 @@
       <c r="P103" t="n">
         <v>33</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0.009454625838138971</v>
       </c>
@@ -22800,9 +22695,6 @@
       <c r="P106" t="n">
         <v>20</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.00573007626553877</v>
       </c>
@@ -23454,9 +23346,6 @@
       <c r="P109" t="n">
         <v>36</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0.01031413727796979</v>
       </c>
@@ -24108,9 +23997,6 @@
       <c r="P112" t="n">
         <v>34</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.00974112965141591</v>
       </c>
@@ -24759,9 +24645,6 @@
       <c r="O115" t="n">
         <v>7</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.02570968273663853</v>
       </c>
@@ -25150,16 +25033,13 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O117" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q117" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R117" t="n">
-        <v>0.06083969425011655</v>
+        <v>0.06518538669655344</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -25312,10 +25192,10 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O118" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="U118" t="inlineStr">
         <is>
@@ -25404,7 +25284,7 @@
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN118" t="b">
@@ -25554,9 +25434,6 @@
       <c r="P119" t="n">
         <v>43</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.01231966397090836</v>
       </c>
@@ -26128,6 +26005,657 @@
         </is>
       </c>
       <c r="BC121" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>急性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>38</v>
+      </c>
+      <c r="O122" t="n">
+        <v>38</v>
+      </c>
+      <c r="P122" t="n">
+        <v>38</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.01088714490452366</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP122" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ122" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT122" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV122" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA122" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB122" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC122" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>急性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>38</v>
+      </c>
+      <c r="O123" t="n">
+        <v>38</v>
+      </c>
+      <c r="P123" t="n">
+        <v>38</v>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>Hepatitis C, acute, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD123" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Confirmed acute hepatitis C component.</t>
+        </is>
+      </c>
+      <c r="AM123" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN123" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP123" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT123" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU123" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV123" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA123" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB123" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC123" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>急性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>7</v>
+      </c>
+      <c r="O124" t="n">
+        <v>7</v>
+      </c>
+      <c r="P124" t="n">
+        <v>7</v>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_PROBABLE</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_PROBABLE</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>Hepatitis C, acute, Probable</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD124" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF124" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG124" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>Probable acute hepatitis C component retained as an independent source series.</t>
+        </is>
+      </c>
+      <c r="AM124" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP124" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ124" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT124" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV124" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA124" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB124" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC124" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -26166,7 +26694,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -26249,7 +26777,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10">
@@ -26259,7 +26787,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11">
@@ -26279,7 +26807,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13">
@@ -26311,7 +26839,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1947</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d210/2026-2029.xlsx
+++ b/diseases/d210/2026-2029.xlsx
@@ -25033,13 +25033,13 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O117" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R117" t="n">
-        <v>0.06518538669655344</v>
+        <v>0.06953107914299034</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -25192,10 +25192,10 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O118" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U118" t="inlineStr">
         <is>
@@ -26839,7 +26839,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d210/2026-2029.xlsx
+++ b/diseases/d210/2026-2029.xlsx
@@ -17860,13 +17860,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O83" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="R83" t="n">
-        <v>0.4076821119666967</v>
+        <v>0.4113549237862165</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -18019,10 +18019,10 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O84" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="U84" t="inlineStr">
         <is>
@@ -24640,13 +24640,13 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="O115" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="R115" t="n">
-        <v>0.02570968273663853</v>
+        <v>0.05141936547327706</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -24799,10 +24799,10 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="O116" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="U116" t="inlineStr">
         <is>
@@ -26839,7 +26839,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1987</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d210/2026-2029.xlsx
+++ b/diseases/d210/2026-2029.xlsx
@@ -24640,13 +24640,13 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O115" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R115" t="n">
-        <v>0.05141936547327706</v>
+        <v>0.05509217729279685</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -24799,10 +24799,10 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O116" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="U116" t="inlineStr">
         <is>
@@ -26839,7 +26839,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1995</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d210/2026-2029.xlsx
+++ b/diseases/d210/2026-2029.xlsx
@@ -21250,13 +21250,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="O99" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="R99" t="n">
-        <v>0.2240415209907072</v>
+        <v>0.2424055800883061</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -21409,10 +21409,10 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="O100" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="U100" t="inlineStr">
         <is>
@@ -24640,13 +24640,13 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="O115" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="R115" t="n">
-        <v>0.05509217729279685</v>
+        <v>0.08814748366847497</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -24799,10 +24799,10 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="O116" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="U116" t="inlineStr">
         <is>
@@ -26839,7 +26839,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1996</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d210/2026-2029.xlsx
+++ b/diseases/d210/2026-2029.xlsx
@@ -18111,7 +18111,7 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN84" t="b">
@@ -21501,7 +21501,7 @@
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN100" t="b">
@@ -24891,7 +24891,7 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN116" t="b">

--- a/diseases/d210/2026-2029.xlsx
+++ b/diseases/d210/2026-2029.xlsx
@@ -26661,6 +26661,657 @@
         </is>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>急性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>36</v>
+      </c>
+      <c r="O125" t="n">
+        <v>36</v>
+      </c>
+      <c r="P125" t="n">
+        <v>36</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.01031413727796979</v>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP125" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT125" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV125" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA125" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB125" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC125" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>急性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>36</v>
+      </c>
+      <c r="O126" t="n">
+        <v>36</v>
+      </c>
+      <c r="P126" t="n">
+        <v>36</v>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>Hepatitis C, acute, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD126" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF126" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG126" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>Confirmed acute hepatitis C component.</t>
+        </is>
+      </c>
+      <c r="AM126" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN126" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP126" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ126" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR126" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT126" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU126" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV126" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA126" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB126" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC126" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>急性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>7</v>
+      </c>
+      <c r="O127" t="n">
+        <v>7</v>
+      </c>
+      <c r="P127" t="n">
+        <v>7</v>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_PROBABLE</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_PROBABLE</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>Hepatitis C, acute, Probable</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD127" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>Probable acute hepatitis C component retained as an independent source series.</t>
+        </is>
+      </c>
+      <c r="AM127" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP127" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT127" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV127" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA127" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB127" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC127" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26694,7 +27345,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -26777,7 +27428,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10">
@@ -26787,7 +27438,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11">
@@ -26807,7 +27458,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13">
@@ -26839,7 +27490,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2010</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d210/2026-2029.xlsx
+++ b/diseases/d210/2026-2029.xlsx
@@ -17860,13 +17860,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O83" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="R83" t="n">
-        <v>0.4113549237862165</v>
+        <v>0.4150277356057363</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -18019,10 +18019,10 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O84" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="U84" t="inlineStr">
         <is>
@@ -27490,7 +27490,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2046</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d210/2026-2029.xlsx
+++ b/diseases/d210/2026-2029.xlsx
@@ -17860,13 +17860,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="O83" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="R83" t="n">
-        <v>0.4150277356057363</v>
+        <v>0.4260461710642957</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -18019,10 +18019,10 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="O84" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="U84" t="inlineStr">
         <is>
@@ -27490,7 +27490,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2047</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d210/2026-2029.xlsx
+++ b/diseases/d210/2026-2029.xlsx
@@ -1166,7 +1166,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5750,7 +5750,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8640,7 +8640,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9443,7 +9443,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10730,7 +10730,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -11687,7 +11687,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12091,7 +12091,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12333,7 +12333,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -13136,7 +13136,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -13378,7 +13378,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -14181,7 +14181,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14423,7 +14423,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -15226,7 +15226,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -16419,7 +16419,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -16823,7 +16823,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -17065,7 +17065,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17868,7 +17868,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18110,7 +18110,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -18913,7 +18913,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -19155,7 +19155,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19958,7 +19958,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -20200,7 +20200,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -21151,7 +21151,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21555,7 +21555,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21797,7 +21797,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -22600,7 +22600,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -22842,7 +22842,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -23645,7 +23645,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23887,7 +23887,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -24690,7 +24690,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -24932,7 +24932,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -25735,7 +25735,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25977,7 +25977,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -26769,7 +26769,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
@@ -27162,7 +27162,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -27566,7 +27566,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -27808,7 +27808,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -28611,7 +28611,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -28853,7 +28853,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -29656,7 +29656,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -29898,7 +29898,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -30701,7 +30701,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30943,7 +30943,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -31735,7 +31735,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
@@ -32128,7 +32128,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -32532,7 +32532,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -33577,7 +33577,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -33819,7 +33819,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -34622,7 +34622,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
@@ -34864,7 +34864,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -35667,7 +35667,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -35909,7 +35909,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
@@ -36701,7 +36701,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
@@ -37094,7 +37094,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -37498,7 +37498,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -37740,7 +37740,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -38543,7 +38543,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -38785,7 +38785,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK186" t="inlineStr">
@@ -39588,7 +39588,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK190" t="inlineStr">
@@ -39830,7 +39830,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -40633,7 +40633,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -40875,7 +40875,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">

--- a/diseases/d210/2026-2029.xlsx
+++ b/diseases/d210/2026-2029.xlsx
@@ -1166,7 +1166,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5750,7 +5750,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8640,7 +8640,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9443,7 +9443,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10730,7 +10730,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -11687,7 +11687,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12091,7 +12091,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12333,7 +12333,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -13136,7 +13136,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -13378,7 +13378,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -14181,7 +14181,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14423,7 +14423,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -15226,7 +15226,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -16419,7 +16419,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -16823,7 +16823,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -17065,7 +17065,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17868,7 +17868,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18110,7 +18110,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -18913,7 +18913,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -19155,7 +19155,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19958,7 +19958,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -20200,7 +20200,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -21151,7 +21151,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21555,7 +21555,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21797,7 +21797,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -22600,7 +22600,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -22842,7 +22842,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -23645,7 +23645,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23887,7 +23887,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -24690,7 +24690,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -24932,7 +24932,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -25735,7 +25735,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25977,7 +25977,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -26769,7 +26769,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
@@ -27162,7 +27162,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -27566,7 +27566,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -27808,7 +27808,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -28611,7 +28611,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -28853,7 +28853,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -29656,7 +29656,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -29898,7 +29898,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -30701,7 +30701,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30943,7 +30943,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -31735,7 +31735,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
@@ -32128,7 +32128,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -32532,7 +32532,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -33577,7 +33577,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -33819,7 +33819,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -34622,7 +34622,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
@@ -34864,7 +34864,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -35667,7 +35667,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -35909,7 +35909,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
@@ -36701,7 +36701,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
@@ -37094,7 +37094,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -37498,7 +37498,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -37740,7 +37740,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -38543,7 +38543,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -38785,7 +38785,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK186" t="inlineStr">
@@ -39588,7 +39588,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK190" t="inlineStr">
@@ -39830,7 +39830,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -40633,7 +40633,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -40875,7 +40875,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">

--- a/diseases/d210/2026-2029.xlsx
+++ b/diseases/d210/2026-2029.xlsx
@@ -26528,13 +26528,13 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="O127" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R127" t="n">
-        <v>0.4260461710642957</v>
+        <v>0.4444102301618946</v>
       </c>
       <c r="S127" t="inlineStr">
         <is>
@@ -26687,10 +26687,10 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="O128" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="U128" t="inlineStr">
         <is>
@@ -41143,7 +41143,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2087</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d210/2026-2029.xlsx
+++ b/diseases/d210/2026-2029.xlsx
@@ -1166,7 +1166,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5750,7 +5750,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8640,7 +8640,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9443,7 +9443,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10730,7 +10730,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -11687,7 +11687,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12091,7 +12091,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12333,7 +12333,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -13136,7 +13136,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -13378,7 +13378,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -14181,7 +14181,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14423,7 +14423,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -15226,7 +15226,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -16419,7 +16419,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -16823,7 +16823,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -17065,7 +17065,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17868,7 +17868,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18110,7 +18110,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -18913,7 +18913,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -19155,7 +19155,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19958,7 +19958,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -20200,7 +20200,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -21151,7 +21151,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21555,7 +21555,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21797,7 +21797,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -22600,7 +22600,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -22842,7 +22842,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -23645,7 +23645,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23887,7 +23887,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -24690,7 +24690,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -24932,7 +24932,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -25735,7 +25735,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25977,7 +25977,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -26769,7 +26769,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
@@ -27162,7 +27162,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -27566,7 +27566,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -27808,7 +27808,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -28611,7 +28611,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -28853,7 +28853,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -29656,7 +29656,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -29898,7 +29898,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -30701,7 +30701,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30943,7 +30943,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -31735,7 +31735,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
@@ -32128,7 +32128,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -32532,7 +32532,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -33577,7 +33577,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -33819,7 +33819,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -34622,7 +34622,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
@@ -34864,7 +34864,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -35667,7 +35667,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -35909,7 +35909,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
@@ -36701,7 +36701,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
@@ -37094,7 +37094,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -37498,7 +37498,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -37740,7 +37740,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -38543,7 +38543,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -38785,7 +38785,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK186" t="inlineStr">
@@ -39588,7 +39588,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK190" t="inlineStr">
@@ -39830,7 +39830,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -40633,7 +40633,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -40875,7 +40875,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">
